--- a/tools/importer/reports/import-installation-files-template.report.xlsx
+++ b/tools/importer/reports/import-installation-files-template.report.xlsx
@@ -52,7 +52,7 @@
     <t>installation-files-template</t>
   </si>
   <si>
-    <t>2026-07-16T13:11:37.643Z</t>
+    <t>2026-07-16T13:57:08.889Z</t>
   </si>
   <si>
     <t>Install AVG Business Edition on your PC | AVG installation files</t>
